--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_398_R44.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_398_R44.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3465</v>
+        <v>7.2315</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4057</v>
+        <v>4.5494</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9407</v>
+        <v>2.6822</v>
       </c>
       <c r="G2" t="n">
         <v>1.6625</v>
@@ -610,13 +610,13 @@
         <v>3.6396</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0886</v>
+        <v>-0.2035</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1554</v>
+        <v>-0.0117</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0668</v>
+        <v>-0.1918</v>
       </c>
       <c r="V2" t="n">
         <v>3.2703</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.7613</v>
+        <v>5.6209</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8361</v>
+        <v>3.6957</v>
       </c>
       <c r="F3" t="n">
         <v>1.9252</v>
@@ -688,10 +688,10 @@
         <v>3.6396</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8381999999999999</v>
+        <v>-0.3022</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4729</v>
+        <v>0.3325</v>
       </c>
       <c r="U3" t="n">
         <v>-0.6347</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7814</v>
+        <v>1.943</v>
       </c>
       <c r="E4" t="n">
         <v>0.4756</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3058</v>
+        <v>1.4674</v>
       </c>
       <c r="G4" t="n">
         <v>1.2785</v>
@@ -766,13 +766,13 @@
         <v>1.1374</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6345</v>
+        <v>-0.4729</v>
       </c>
       <c r="T4" t="n">
         <v>-0.431</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2036</v>
+        <v>-0.0419</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3302</v>
+        <v>-1.7987</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1913</v>
+        <v>-1.7243</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.139</v>
+        <v>-0.0743</v>
       </c>
       <c r="G8" t="n">
         <v>-3.5467</v>
@@ -1078,13 +1078,13 @@
         <v>2.2747</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0583</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2153</v>
+        <v>0.2516</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.843</v>
+        <v>-0.7783</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4069</v>
+        <v>-2.1505</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7547</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6522</v>
+        <v>-1.5472</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9624</v>
+        <v>-0.2084</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8116</v>
+        <v>-1.2249</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1508</v>
+        <v>1.0165</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5392</v>
+        <v>1.7575</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.761</v>
+        <v>0.9298</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7782</v>
+        <v>0.8277</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4232</v>
+        <v>-1.9659</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0506</v>
+        <v>-2.1547</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3725</v>
+        <v>0.1888</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-2.5022</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.4121</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.9099</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1006</v>
+        <v>0.015</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2155</v>
+        <v>-0.0388</v>
       </c>
       <c r="U9" t="n">
-        <v>0.316</v>
+        <v>0.0538</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5451</v>
+        <v>0.5451</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0901</v>
       </c>
       <c r="X9" t="n">
         <v>-0.5451</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5079</v>
+        <v>-2.3548</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8637</v>
+        <v>-1.638</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6442</v>
+        <v>-0.7168</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2084</v>
+        <v>-1.9624</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2249</v>
+        <v>-0.8116</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0165</v>
+        <v>-1.1508</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7575</v>
+        <v>-1.5392</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9298</v>
+        <v>-0.761</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8277</v>
+        <v>-0.7782</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9659</v>
+        <v>-0.4232</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.1547</v>
+        <v>-0.0506</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1888</v>
+        <v>-0.3725</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.5022</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4121</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9099</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3423</v>
+        <v>0.1526</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2992</v>
+        <v>-0.0987</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0432</v>
+        <v>0.2514</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5451</v>
+        <v>-0.5451</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0901</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-0.5451</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. EDWARDS</t>
+          <t>L. RANDOLPH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0258</v>
+        <v>-2.9888</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1116</v>
+        <v>-1.6616</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9142</v>
+        <v>-1.3271</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.774</v>
+        <v>-1.6234</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.5754</v>
+        <v>-2.4521</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8014</v>
+        <v>0.8288</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3312</v>
+        <v>-0.3808</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.8708</v>
+        <v>-1.6101</v>
       </c>
       <c r="L11" t="n">
-        <v>2.202</v>
+        <v>1.2293</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1052</v>
+        <v>-1.2426</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7047</v>
+        <v>-0.842</v>
       </c>
       <c r="O11" t="n">
         <v>-0.4006</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8198</v>
+        <v>0.6824</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R11" t="n">
         <v>1.8198</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1987</v>
+        <v>-0.9577</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4428</v>
+        <v>-0.1435</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6415999999999999</v>
+        <v>-0.8142</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.2703</v>
+        <v>-1.0901</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.2703</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. RANDOLPH</t>
+          <t>E. BRYANT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2473</v>
+        <v>-3.4249</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6616</v>
+        <v>-2.6798</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5857</v>
+        <v>-0.7451</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.6234</v>
+        <v>-5.2687</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.4521</v>
+        <v>-6.0643</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8288</v>
+        <v>0.7956</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3808</v>
+        <v>-2.7735</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.6101</v>
+        <v>-4.309</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2293</v>
+        <v>1.5355</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2426</v>
+        <v>-2.4952</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.842</v>
+        <v>-1.7553</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4006</v>
+        <v>-0.7399</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6824</v>
+        <v>2.7297</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.1374</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8198</v>
+        <v>3.867</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2163</v>
+        <v>-0.8859</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1435</v>
+        <v>-0.5625</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0728</v>
+        <v>-0.3234</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.7935</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0901</v>
+        <v>-1.7935</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. BRYANT</t>
+          <t>K. EDWARDS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.5024</v>
+        <v>-3.4909</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.7573</v>
+        <v>-0.3181</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7451</v>
+        <v>-3.1728</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.2687</v>
+        <v>-1.774</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.0643</v>
+        <v>-3.5754</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7956</v>
+        <v>1.8014</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.7735</v>
+        <v>0.3312</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.309</v>
+        <v>-1.8708</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5355</v>
+        <v>2.202</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.4952</v>
+        <v>-2.1052</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.7553</v>
+        <v>-1.7047</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7399</v>
+        <v>-0.4006</v>
       </c>
       <c r="P13" t="n">
-        <v>2.7297</v>
+        <v>1.8198</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.867</v>
+        <v>1.8198</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.9634</v>
+        <v>-0.2664</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.64</v>
+        <v>-0.6494</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3234</v>
+        <v>0.383</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-3.2703</v>
       </c>
       <c r="W13" t="n">
-        <v>1.7935</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.7935</v>
+        <v>-3.2703</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.947799999999999</v>
+        <v>-4.229700000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.886499999999999</v>
+        <v>-1.168099999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.0614</v>
+        <v>-3.0612</v>
       </c>
       <c r="G14" t="n">
         <v>-10.1485</v>
@@ -1519,13 +1519,13 @@
         <v>2.6409</v>
       </c>
       <c r="J14" t="n">
-        <v>2.749500000000001</v>
+        <v>2.7495</v>
       </c>
       <c r="K14" t="n">
         <v>-2.8128</v>
       </c>
       <c r="L14" t="n">
-        <v>5.5622</v>
+        <v>5.562200000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-12.898</v>
@@ -1546,13 +1546,13 @@
         <v>19.3353</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.3096</v>
+        <v>-3.5914</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.2135</v>
+        <v>-1.4952</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.0963</v>
+        <v>-2.0961</v>
       </c>
       <c r="V14" t="n">
         <v>-1.8635</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1499</v>
+        <v>4.8386</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0143</v>
+        <v>3.5474</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1356</v>
+        <v>1.2913</v>
       </c>
       <c r="G15" t="n">
         <v>4.8513</v>
@@ -1624,13 +1624,13 @@
         <v>1.1374</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3887</v>
+        <v>1.0774</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0537</v>
+        <v>0.5867</v>
       </c>
       <c r="U15" t="n">
-        <v>0.335</v>
+        <v>0.4906</v>
       </c>
       <c r="V15" t="n">
         <v>-1.0901</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.379</v>
+        <v>4.5029</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6542</v>
+        <v>2.0044</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7248</v>
+        <v>2.4985</v>
       </c>
       <c r="G16" t="n">
         <v>3.6517</v>
@@ -1702,13 +1702,13 @@
         <v>1.1374</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3878</v>
+        <v>0.5117</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.431</v>
+        <v>-0.0808</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8187</v>
+        <v>0.5925</v>
       </c>
       <c r="V16" t="n">
         <v>1.4768</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1703</v>
+        <v>3.2344</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7856</v>
+        <v>2.4354</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3848</v>
+        <v>0.799</v>
       </c>
       <c r="G17" t="n">
         <v>0.5837</v>
@@ -1780,13 +1780,13 @@
         <v>0.2275</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4957</v>
+        <v>0.5597</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0537</v>
+        <v>0.7035</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.1438</v>
       </c>
       <c r="V17" t="n">
         <v>1.8635</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2027</v>
+        <v>2.2153</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0071</v>
+        <v>-0.1238</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2098</v>
+        <v>2.3391</v>
       </c>
       <c r="G18" t="n">
         <v>1.9636</v>
@@ -1858,13 +1858,13 @@
         <v>1.1374</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3975</v>
+        <v>0.41</v>
       </c>
       <c r="T18" t="n">
-        <v>0.06</v>
+        <v>-0.0568</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3375</v>
+        <v>0.4668</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1583</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.1142</v>
+        <v>1.2522</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3913</v>
+        <v>-0.3091</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7229</v>
+        <v>1.5612</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8669</v>
@@ -1936,13 +1936,13 @@
         <v>1.3648</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6162</v>
+        <v>0.7542</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7664</v>
+        <v>0.066</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8498</v>
+        <v>0.6882</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7996</v>
+        <v>-0.2291</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0592</v>
+        <v>-1.709</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2596</v>
+        <v>1.4799</v>
       </c>
       <c r="G21" t="n">
         <v>1.9563</v>
@@ -2092,13 +2092,13 @@
         <v>1.1374</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6395</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5028</v>
+        <v>-0.1526</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1367</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>0.1583</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0133</v>
+        <v>-0.4173</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6787</v>
+        <v>0.4933</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6654</v>
+        <v>-0.9106</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0603</v>
+        <v>-0.1189</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1219</v>
+        <v>-0.2067</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1822</v>
+        <v>0.0878</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1822</v>
+        <v>1.3243</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>-0.2816</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1822</v>
+        <v>1.6059</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1219</v>
+        <v>-1.4432</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1219</v>
+        <v>0.075</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-1.5182</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9099</v>
+        <v>-2.9572</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1374</v>
+        <v>-3.4121</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2275</v>
+        <v>0.4549</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0431</v>
+        <v>0.3202</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3591</v>
+        <v>0.2425</v>
       </c>
       <c r="U22" t="n">
-        <v>0.316</v>
+        <v>0.0776</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2.3386</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.3386</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2554</v>
+        <v>-0.8445</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7851</v>
+        <v>-1.4452</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0405</v>
+        <v>0.6008</v>
       </c>
       <c r="G23" t="n">
-        <v>2.1032</v>
+        <v>-0.0603</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6761</v>
+        <v>0.1219</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4271</v>
+        <v>-0.1822</v>
       </c>
       <c r="J23" t="n">
-        <v>3.7358</v>
+        <v>-0.1822</v>
       </c>
       <c r="K23" t="n">
-        <v>1.7905</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1.9453</v>
+        <v>-0.1822</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6326</v>
+        <v>0.1219</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1144</v>
+        <v>0.1219</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.5182</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.9572</v>
+        <v>-0.9099</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4121</v>
+        <v>-1.1374</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4549</v>
+        <v>0.2275</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1436</v>
+        <v>0.1257</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0837</v>
+        <v>-0.1257</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2273</v>
+        <v>0.2514</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5451</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5451</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,37 +2281,37 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3578</v>
+        <v>-0.9111</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3239</v>
+        <v>1.1353</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0339</v>
+        <v>-2.0464</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1189</v>
+        <v>2.1032</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2067</v>
+        <v>1.6761</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0878</v>
+        <v>0.4271</v>
       </c>
       <c r="J24" t="n">
-        <v>1.3243</v>
+        <v>3.7358</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2816</v>
+        <v>1.7905</v>
       </c>
       <c r="L24" t="n">
-        <v>1.6059</v>
+        <v>1.9453</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4432</v>
+        <v>-1.6326</v>
       </c>
       <c r="N24" t="n">
-        <v>0.075</v>
+        <v>-0.1144</v>
       </c>
       <c r="O24" t="n">
         <v>-1.5182</v>
@@ -2326,22 +2326,22 @@
         <v>0.4549</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6203</v>
+        <v>0.4878</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5746</v>
+        <v>0.2665</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0457</v>
+        <v>0.2213</v>
       </c>
       <c r="V24" t="n">
-        <v>2.3386</v>
+        <v>-0.5451</v>
       </c>
       <c r="W24" t="n">
-        <v>2.3386</v>
+        <v>0.5451</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.2096</v>
+        <v>-2.6963</v>
       </c>
       <c r="E25" t="n">
-        <v>0.117</v>
+        <v>-0.4666</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3266</v>
+        <v>-2.2297</v>
       </c>
       <c r="G25" t="n">
         <v>-1.1603</v>
@@ -2404,13 +2404,13 @@
         <v>0.4549</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7232</v>
+        <v>0.2365</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7664</v>
+        <v>0.1827</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0432</v>
+        <v>0.0538</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0901</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.5883</v>
+        <v>-5.3746</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.1624</v>
+        <v>-3.0457</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.4259</v>
+        <v>-2.329</v>
       </c>
       <c r="G26" t="n">
         <v>-2.9107</v>
@@ -2482,13 +2482,13 @@
         <v>0.2275</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4598</v>
+        <v>0.6735</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3473</v>
+        <v>0.464</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1125</v>
+        <v>0.2094</v>
       </c>
       <c r="V26" t="n">
         <v>-1.0901</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>4.947700000000003</v>
+        <v>5.7261</v>
       </c>
       <c r="E27" t="n">
-        <v>2.516199999999999</v>
+        <v>2.516400000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>2.4316</v>
+        <v>3.209699999999998</v>
       </c>
       <c r="G27" t="n">
         <v>10.1483</v>
@@ -2536,7 +2536,7 @@
         <v>12.8981</v>
       </c>
       <c r="K27" t="n">
-        <v>9.976599999999999</v>
+        <v>9.976599999999998</v>
       </c>
       <c r="L27" t="n">
         <v>2.9214</v>
@@ -2557,19 +2557,19 @@
         <v>-19.3353</v>
       </c>
       <c r="R27" t="n">
-        <v>7.961600000000002</v>
+        <v>7.961600000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>4.3096</v>
+        <v>5.0877</v>
       </c>
       <c r="T27" t="n">
-        <v>2.0963</v>
+        <v>2.096</v>
       </c>
       <c r="U27" t="n">
-        <v>2.2132</v>
+        <v>2.9914</v>
       </c>
       <c r="V27" t="n">
-        <v>1.863499999999999</v>
+        <v>1.8635</v>
       </c>
       <c r="W27" t="n">
         <v>6.8574</v>
